--- a/Control_Inventario_Pole_Dance.xlsx
+++ b/Control_Inventario_Pole_Dance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Winberthey Gaitan Hernandez\OneDrive - CENICANA\Escritorio\Academia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cenicanaoff365-my.sharepoint.com/personal/iavar3_cenicanaoff365_onmicrosoft_com/Documents/Escritorio/Academia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD43FD3-F47E-4905-87FE-0927DD75E0EC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="24220" windowHeight="13000" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📊 Dashboard Control" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
   <si>
     <t>PANEL DE CONTROL E INVENTARIOS - POLE DANCE ACADEMY</t>
   </si>
@@ -565,9 +565,6 @@
     <t>ACT-008</t>
   </si>
   <si>
-    <t>Sistema de Sonido Bluetooth 200W</t>
-  </si>
-  <si>
     <t>2025-01-12</t>
   </si>
   <si>
@@ -626,6 +623,18 @@
   </si>
   <si>
     <t>ACT-009</t>
+  </si>
+  <si>
+    <t>Barra / Pole Profesional Plateado</t>
+  </si>
+  <si>
+    <t>Espuma + casata</t>
+  </si>
+  <si>
+    <t>Colchoneta de Caída para Pole espuma + casata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema de Sonido </t>
   </si>
 </sst>
 </file>
@@ -837,26 +846,30 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -865,15 +878,11 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,19 +990,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1189,13 +1198,13 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>175000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>85000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1606,101 +1615,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
     </row>
     <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="24"/>
+      <c r="D4" s="27"/>
     </row>
     <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="23" t="str">
+      <c r="B5" s="27"/>
+      <c r="C5" s="31" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "⚠️ Código no encontrado")</f>
         <v>Top Velvet Negro</v>
       </c>
-      <c r="D5" s="24"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="23" t="str">
+      <c r="B6" s="27"/>
+      <c r="C6" s="31" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "-")</f>
         <v>M</v>
       </c>
-      <c r="D6" s="24"/>
+      <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="32">
+      <c r="B7" s="27"/>
+      <c r="C7" s="34">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>55000</v>
       </c>
-      <c r="D7" s="24"/>
+      <c r="D7" s="27"/>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="30">
+      <c r="B8" s="27"/>
+      <c r="C8" s="29">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:J, 10, FALSE), 0)</f>
-        <v>15</v>
-      </c>
-      <c r="D8" s="24"/>
+        <v>2</v>
+      </c>
+      <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="30">
+      <c r="B9" s="27"/>
+      <c r="C9" s="29">
         <f>SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F)</f>
-        <v>2</v>
-      </c>
-      <c r="D9" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="D9" s="27"/>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="29" t="str">
+      <c r="B10" s="27"/>
+      <c r="C10" s="36" t="str">
         <f>IF(C4="","", C4 &amp; (SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F) + 1))</f>
-        <v>TM3</v>
-      </c>
-      <c r="D10" s="24"/>
+        <v>TM1</v>
+      </c>
+      <c r="D10" s="27"/>
     </row>
     <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
@@ -1708,54 +1717,54 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="27"/>
+      <c r="C14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="26" t="s">
+      <c r="D14" s="27"/>
+      <c r="E14" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="26" t="s">
+      <c r="F14" s="27"/>
+      <c r="G14" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="24"/>
+      <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="31">
+      <c r="A15" s="33">
         <f>SUM('🏷️ Catálogo Productos'!J4:J14)</f>
-        <v>131</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25">
+        <v>14</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="26">
         <f>SUM('🏷️ Catálogo Productos'!K4:K14)</f>
-        <v>3545000</v>
-      </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="25">
+        <v>405000</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="26">
         <f>SUM('🛒 Ventas'!H4:H60)</f>
-        <v>295000</v>
-      </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="25">
-        <f>SUM('🏢 Activos Fijos'!H4:H12)</f>
-        <v>3100000</v>
-      </c>
-      <c r="H15" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="27"/>
+      <c r="G15" s="26">
+        <f>SUM('🏢 Activos Fijos'!H4:H13)</f>
+        <v>4150000</v>
+      </c>
+      <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
     </row>
     <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
@@ -1791,11 +1800,11 @@
       </c>
       <c r="B22" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, "S*", '🛒 Ventas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="8">
         <f>SUMIF('🛒 Ventas'!C:C, "S*", '🛒 Ventas'!H:H)</f>
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>24</v>
@@ -1806,7 +1815,7 @@
       </c>
       <c r="G22" s="8">
         <f>SUMIF('🛒 Ventas'!I:I, "Nequi", '🛒 Ventas'!H:H)</f>
-        <v>175000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1815,11 +1824,11 @@
       </c>
       <c r="B23" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, "P*", '🛒 Ventas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="8">
         <f>SUMIF('🛒 Ventas'!C:C, "P*", '🛒 Ventas'!H:H)</f>
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>26</v>
@@ -1830,7 +1839,7 @@
       </c>
       <c r="G23" s="8">
         <f>SUMIF('🛒 Ventas'!I:I, "Daviplata", '🛒 Ventas'!H:H)</f>
-        <v>35000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1839,11 +1848,11 @@
       </c>
       <c r="B24" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, "T*", '🛒 Ventas'!F:F)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" s="8">
         <f>SUMIF('🛒 Ventas'!C:C, "T*", '🛒 Ventas'!H:H)</f>
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>28</v>
@@ -1854,7 +1863,7 @@
       </c>
       <c r="G24" s="8">
         <f>SUMIF('🛒 Ventas'!I:I, "Efectivo", '🛒 Ventas'!H:H)</f>
-        <v>85000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1887,11 +1896,11 @@
       </c>
       <c r="B26" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, "A*", '🛒 Ventas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="8">
         <f>SUMIF('🛒 Ventas'!C:C, "A*", '🛒 Ventas'!H:H)</f>
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>32</v>
@@ -1911,11 +1920,11 @@
       </c>
       <c r="B27" s="10">
         <f>SUM(B22:B26)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C27" s="11">
         <f>SUM(C22:C26)</f>
-        <v>295000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>33</v>
@@ -1926,7 +1935,7 @@
       </c>
       <c r="G27" s="11">
         <f>SUM(G22:G26)</f>
-        <v>295000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1947,14 +1956,14 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E15:F16"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -2118,20 +2127,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -2191,27 +2200,27 @@
         <v>55000</v>
       </c>
       <c r="G4" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A4, '📥 Entradas'!F:F)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, A4, '🛒 Ventas'!F:F)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4:J14" si="0">G4+H4-I4</f>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K4" s="8">
         <f t="shared" ref="K4:K14" si="1">J4*E4</f>
-        <v>375000</v>
+        <v>50000</v>
       </c>
       <c r="L4" s="15" t="str">
         <f t="shared" ref="L4:L14" si="2">IF(J4&lt;=0, "❌ Agotado", IF(J4&lt;=3, "⚠️ Stock Bajo", "✅ Disponible"))</f>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2233,8 +2242,8 @@
       <c r="F5" s="18">
         <v>55000</v>
       </c>
-      <c r="G5" s="19">
-        <v>10</v>
+      <c r="G5" s="7">
+        <v>1</v>
       </c>
       <c r="H5" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A5, '📥 Entradas'!F:F)</f>
@@ -2246,15 +2255,15 @@
       </c>
       <c r="J5" s="20">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K5" s="18">
         <f t="shared" si="1"/>
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="L5" s="16" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2277,7 +2286,7 @@
         <v>55000</v>
       </c>
       <c r="G6" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A6, '📥 Entradas'!F:F)</f>
@@ -2289,15 +2298,15 @@
       </c>
       <c r="J6" s="3">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K6" s="8">
         <f t="shared" si="1"/>
-        <v>200000</v>
+        <v>25000</v>
       </c>
       <c r="L6" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2319,28 +2328,28 @@
       <c r="F7" s="18">
         <v>65000</v>
       </c>
-      <c r="G7" s="19">
-        <v>15</v>
+      <c r="G7" s="7">
+        <v>1</v>
       </c>
       <c r="H7" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A7, '📥 Entradas'!F:F)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="19">
         <f>SUMIF('🛒 Ventas'!C:C, A7, '🛒 Ventas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="20">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>570000</v>
+        <v>60000</v>
       </c>
       <c r="L7" s="16" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2363,7 +2372,7 @@
         <v>65000</v>
       </c>
       <c r="G8" s="7">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A8, '📥 Entradas'!F:F)</f>
@@ -2375,15 +2384,15 @@
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K8" s="8">
         <f t="shared" si="1"/>
-        <v>450000</v>
+        <v>30000</v>
       </c>
       <c r="L8" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2405,8 +2414,8 @@
       <c r="F9" s="18">
         <v>65000</v>
       </c>
-      <c r="G9" s="19">
-        <v>10</v>
+      <c r="G9" s="7">
+        <v>1</v>
       </c>
       <c r="H9" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A9, '📥 Entradas'!F:F)</f>
@@ -2418,15 +2427,15 @@
       </c>
       <c r="J9" s="20">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K9" s="18">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="L9" s="16" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2449,7 +2458,7 @@
         <v>85000</v>
       </c>
       <c r="G10" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A10, '📥 Entradas'!F:F)</f>
@@ -2457,19 +2466,19 @@
       </c>
       <c r="I10" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, A10, '🛒 Ventas'!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
       </c>
       <c r="K10" s="8">
         <f t="shared" si="1"/>
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="L10" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2491,8 +2500,8 @@
       <c r="F11" s="18">
         <v>85000</v>
       </c>
-      <c r="G11" s="19">
-        <v>8</v>
+      <c r="G11" s="7">
+        <v>1</v>
       </c>
       <c r="H11" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A11, '📥 Entradas'!F:F)</f>
@@ -2504,15 +2513,15 @@
       </c>
       <c r="J11" s="20">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K11" s="18">
         <f t="shared" si="1"/>
-        <v>320000</v>
+        <v>40000</v>
       </c>
       <c r="L11" s="16" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2535,7 +2544,7 @@
         <v>85000</v>
       </c>
       <c r="G12" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A12, '📥 Entradas'!F:F)</f>
@@ -2547,15 +2556,15 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K12" s="8">
         <f t="shared" si="1"/>
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="L12" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2577,8 +2586,8 @@
       <c r="F13" s="18">
         <v>75000</v>
       </c>
-      <c r="G13" s="19">
-        <v>7</v>
+      <c r="G13" s="7">
+        <v>1</v>
       </c>
       <c r="H13" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A13, '📥 Entradas'!F:F)</f>
@@ -2590,15 +2599,15 @@
       </c>
       <c r="J13" s="20">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K13" s="18">
         <f t="shared" si="1"/>
-        <v>245000</v>
+        <v>35000</v>
       </c>
       <c r="L13" s="16" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2621,27 +2630,27 @@
         <v>35000</v>
       </c>
       <c r="G14" s="7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A14, '📥 Entradas'!F:F)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I14" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, A14, '🛒 Ventas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K14" s="8">
         <f t="shared" si="1"/>
-        <v>435000</v>
+        <v>30000</v>
       </c>
       <c r="L14" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>✅ Disponible</v>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -2653,25 +2662,22 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="10">
-        <f>SUM(G4:G14)</f>
-        <v>116</v>
-      </c>
+      <c r="G15" s="10"/>
       <c r="H15" s="10">
         <f>SUM(H4:H14)</f>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I15" s="10">
         <f>SUM(I4:I14)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" s="10">
         <f>SUM(J4:J14)</f>
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="K15" s="11">
         <f>SUM(K4:K14)</f>
-        <v>3545000</v>
+        <v>405000</v>
       </c>
       <c r="L15" s="9"/>
     </row>
@@ -2698,17 +2704,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -2758,7 +2764,7 @@
         <v>M</v>
       </c>
       <c r="F4" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4" s="8">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
@@ -2766,7 +2772,7 @@
       </c>
       <c r="H4" s="8">
         <f>F4*G4</f>
-        <v>125000</v>
+        <v>25000</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>93</v>
@@ -2791,7 +2797,7 @@
         <v>M</v>
       </c>
       <c r="F5" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="8">
         <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
@@ -2799,7 +2805,7 @@
       </c>
       <c r="H5" s="8">
         <f>F5*G5</f>
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>93</v>
@@ -2824,7 +2830,7 @@
         <v>Única</v>
       </c>
       <c r="F6" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G6" s="8">
         <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
@@ -2832,7 +2838,7 @@
       </c>
       <c r="H6" s="8">
         <f>F6*G6</f>
-        <v>150000</v>
+        <v>15000</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>97</v>
@@ -3450,18 +3456,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -3514,16 +3520,14 @@
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
         <v>M</v>
       </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="8">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>55000</v>
       </c>
       <c r="H4" s="8">
         <f>F4*G4</f>
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>24</v>
@@ -3551,16 +3555,14 @@
         <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
         <v>M</v>
       </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
+      <c r="F5" s="7"/>
       <c r="G5" s="8">
         <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>65000</v>
       </c>
       <c r="H5" s="8">
         <f>F5*G5</f>
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>24</v>
@@ -3588,16 +3590,14 @@
         <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
         <v>S</v>
       </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
+      <c r="F6" s="7"/>
       <c r="G6" s="8">
         <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>85000</v>
       </c>
       <c r="H6" s="8">
         <f>F6*G6</f>
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>28</v>
@@ -3625,16 +3625,14 @@
         <f>IFERROR(VLOOKUP(C7, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
         <v>Única</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
+      <c r="F7" s="7"/>
       <c r="G7" s="8">
         <f>IFERROR(VLOOKUP(C7, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>35000</v>
       </c>
       <c r="H7" s="8">
         <f>F7*G7</f>
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>26</v>
@@ -3662,16 +3660,14 @@
         <f>IFERROR(VLOOKUP(C8, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
         <v>M</v>
       </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
+      <c r="F8" s="7"/>
       <c r="G8" s="8">
         <f>IFERROR(VLOOKUP(C8, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>55000</v>
       </c>
       <c r="H8" s="8">
         <f>F8*G8</f>
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>24</v>
@@ -4565,7 +4561,7 @@
         <v/>
       </c>
       <c r="H41" s="22" t="str">
-        <f t="shared" ref="H41:H72" si="1">IF(F41="","",F41*G41)</f>
+        <f t="shared" ref="H41:H59" si="1">IF(F41="","",F41*G41)</f>
         <v/>
       </c>
       <c r="I41" s="1"/>
@@ -5089,7 +5085,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
@@ -5101,18 +5097,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -5151,7 +5147,7 @@
         <v>145</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>42</v>
@@ -5169,7 +5165,7 @@
         <v>1200000</v>
       </c>
       <c r="H4" s="8">
-        <f t="shared" ref="H4:H10" si="0">E4*G4</f>
+        <f t="shared" ref="H4:H5" si="0">E4*G4</f>
         <v>2400000</v>
       </c>
       <c r="I4" s="15" t="s">
@@ -5183,8 +5179,8 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>194</v>
+      <c r="B5" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>42</v>
@@ -5193,7 +5189,7 @@
         <v>146</v>
       </c>
       <c r="E5" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>41</v>
@@ -5203,7 +5199,7 @@
       </c>
       <c r="H5" s="18">
         <f t="shared" si="0"/>
-        <v>350000</v>
+        <v>1050000</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>147</v>
@@ -5217,7 +5213,7 @@
         <v>151</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>42</v>
@@ -5249,205 +5245,224 @@
       <c r="A7" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="7"/>
+      <c r="B7" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
       <c r="F7" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="8">
-        <v>15000</v>
-      </c>
-      <c r="H7" s="8">
-        <f>E7*G7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>155</v>
+      <c r="G7" s="18">
+        <v>350000</v>
+      </c>
+      <c r="H7" s="18">
+        <f t="shared" ref="H7" si="2">E7*G7</f>
+        <v>350000</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" s="19"/>
+      <c r="B8" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="7"/>
       <c r="F8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="18">
-        <v>45000</v>
-      </c>
-      <c r="H8" s="18">
-        <f>E8*G8</f>
+      <c r="G8" s="8">
+        <v>15000</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" ref="H8:H13" si="3">E8*G8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>160</v>
+      <c r="I8" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" s="7"/>
+      <c r="B9" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="19"/>
       <c r="F9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="8">
-        <v>60000</v>
-      </c>
-      <c r="H9" s="8">
-        <f>E9*G9</f>
+      <c r="G9" s="18">
+        <v>45000</v>
+      </c>
+      <c r="H9" s="18">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I9" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>164</v>
+      <c r="I9" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="19"/>
+      <c r="B10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="7"/>
       <c r="F10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="18">
-        <v>450000</v>
-      </c>
-      <c r="H10" s="18">
-        <f>E10*G10</f>
+      <c r="G10" s="8">
+        <v>60000</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I10" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>168</v>
+      <c r="I10" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" s="7"/>
+      <c r="B11" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="19"/>
       <c r="F11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="8">
-        <v>80000</v>
-      </c>
-      <c r="H11" s="8">
-        <f>E11*G11</f>
+      <c r="G11" s="18">
+        <v>450000</v>
+      </c>
+      <c r="H11" s="18">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I11" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>173</v>
+      <c r="I11" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="19"/>
+        <v>194</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="7"/>
       <c r="F12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="18">
-        <v>850000</v>
-      </c>
-      <c r="H12" s="18">
-        <f>E12*G12</f>
+      <c r="G12" s="8">
+        <v>80000</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I12" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>177</v>
+      <c r="I12" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
+        <v>178</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>146</v>
+      </c>
       <c r="E13" s="19"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="36"/>
+      <c r="F13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="18">
+        <v>850000</v>
+      </c>
+      <c r="H13" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -5457,11 +5472,11 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="16"/>
-      <c r="J14" s="36"/>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -5471,11 +5486,11 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="16"/>
-      <c r="J15" s="36"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -5485,11 +5500,11 @@
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="16"/>
-      <c r="J16" s="36"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -5499,11 +5514,11 @@
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="16"/>
-      <c r="J17" s="36"/>
+      <c r="J17" s="23"/>
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -5513,11 +5528,11 @@
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
       <c r="I18" s="16"/>
-      <c r="J18" s="36"/>
+      <c r="J18" s="23"/>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -5527,11 +5542,11 @@
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="16"/>
-      <c r="J19" s="36"/>
+      <c r="J19" s="23"/>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -5541,11 +5556,11 @@
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
       <c r="I20" s="16"/>
-      <c r="J20" s="36"/>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -5558,35 +5573,35 @@
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J22" s="9"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E23" s="10">
-        <f>SUM(E4:E12)</f>
-        <v>4</v>
+        <f>SUM(E4:E13)</f>
+        <v>7</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="11">
-        <f>SUM(H4:H12)</f>
-        <v>3100000</v>
+        <f>SUM(H4:H13)</f>
+        <v>4150000</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5595,7 +5610,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="22" t="str">
-        <f t="shared" ref="H24:H37" si="2">IF(E24="","",E24*G24)</f>
+        <f t="shared" ref="H24:H37" si="4">IF(E24="","",E24*G24)</f>
         <v/>
       </c>
       <c r="I24" s="1"/>
@@ -5603,7 +5618,7 @@
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5612,7 +5627,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I25" s="1"/>
@@ -5620,7 +5635,7 @@
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5629,7 +5644,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I26" s="1"/>
@@ -5637,7 +5652,7 @@
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5646,7 +5661,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I27" s="1"/>
@@ -5654,7 +5669,7 @@
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5663,7 +5678,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I28" s="1"/>
@@ -5671,7 +5686,7 @@
     </row>
     <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5680,7 +5695,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I29" s="1"/>
@@ -5688,7 +5703,7 @@
     </row>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5697,7 +5712,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I30" s="1"/>
@@ -5705,7 +5720,7 @@
     </row>
     <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5714,7 +5729,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I31" s="1"/>
@@ -5722,7 +5737,7 @@
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5731,7 +5746,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I32" s="1"/>
@@ -5739,7 +5754,7 @@
     </row>
     <row r="33" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5748,7 +5763,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I33" s="1"/>
@@ -5756,7 +5771,7 @@
     </row>
     <row r="34" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5765,7 +5780,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I34" s="1"/>
@@ -5773,7 +5788,7 @@
     </row>
     <row r="35" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -5782,7 +5797,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I35" s="1"/>
@@ -5790,7 +5805,7 @@
     </row>
     <row r="36" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -5799,7 +5814,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I36" s="1"/>
@@ -5807,7 +5822,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -5816,7 +5831,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I37" s="1"/>

--- a/Control_Inventario_Pole_Dance.xlsx
+++ b/Control_Inventario_Pole_Dance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cenicanaoff365-my.sharepoint.com/personal/iavar3_cenicanaoff365_onmicrosoft_com/Documents/Escritorio/Academia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD43FD3-F47E-4905-87FE-0927DD75E0EC}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A9FECFD-AF0B-4891-848D-55B74A6FD964}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="24220" windowHeight="13000" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📊 Dashboard Control" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="195">
   <si>
     <t>PANEL DE CONTROL E INVENTARIOS - POLE DANCE ACADEMY</t>
   </si>
@@ -205,9 +205,6 @@
     <t>Única</t>
   </si>
   <si>
-    <t>CATÁLOGO MASTER DE PRODUCTOS E INVENTARIO</t>
-  </si>
-  <si>
     <t>SKU / Código</t>
   </si>
   <si>
@@ -289,9 +286,6 @@
     <t>TOTALES INVENTARIO</t>
   </si>
   <si>
-    <t>REGISTRO DE ENTRADAS Y REPOSICIONES DE INVENTARIO</t>
-  </si>
-  <si>
     <t>ID Entrada</t>
   </si>
   <si>
@@ -403,9 +397,6 @@
     <t>ENT-026</t>
   </si>
   <si>
-    <t>REGISTRO DIARIO DE VENTAS Y SALIDAS DE INVENTARIO</t>
-  </si>
-  <si>
     <t>Ref Venta (Consecutivo)</t>
   </si>
   <si>
@@ -440,9 +431,6 @@
   </si>
   <si>
     <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>INVENTARIO DE ACTIVOS FIJOS Y EQUIPAMIENTO DE LA ACADEMIA</t>
   </si>
   <si>
     <t>Código Activo</t>
@@ -853,26 +841,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -882,6 +867,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1628,7 +1616,7 @@
       <c r="I1" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="27"/>
@@ -1636,76 +1624,76 @@
       <c r="D3" s="27"/>
     </row>
     <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="28" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="27"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="27"/>
     </row>
     <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="27"/>
-      <c r="C5" s="31" t="str">
+      <c r="C5" s="36" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "⚠️ Código no encontrado")</f>
         <v>Top Velvet Negro</v>
       </c>
       <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="28" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="27"/>
-      <c r="C6" s="31" t="str">
+      <c r="C6" s="36" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "-")</f>
         <v>M</v>
       </c>
       <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="28" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="27"/>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>55000</v>
       </c>
       <c r="D7" s="27"/>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="28" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="27"/>
-      <c r="C8" s="29">
+      <c r="C8" s="32">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:J, 10, FALSE), 0)</f>
         <v>2</v>
       </c>
       <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="28" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="27"/>
-      <c r="C9" s="29">
+      <c r="C9" s="32">
         <f>SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F)</f>
         <v>0</v>
       </c>
       <c r="D9" s="27"/>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="27"/>
-      <c r="C10" s="36" t="str">
+      <c r="C10" s="35" t="str">
         <f>IF(C4="","", C4 &amp; (SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F) + 1))</f>
         <v>TM1</v>
       </c>
@@ -1717,41 +1705,41 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="31" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="27"/>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="31" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="27"/>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="31" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="27"/>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="31" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="33">
-        <f>SUM('🏷️ Catálogo Productos'!J4:J14)</f>
+      <c r="A15" s="29">
+        <f>SUM('🏷️ Catálogo Productos'!J2:J12)</f>
         <v>14</v>
       </c>
       <c r="B15" s="27"/>
-      <c r="C15" s="26">
-        <f>SUM('🏷️ Catálogo Productos'!K4:K14)</f>
+      <c r="C15" s="30">
+        <f>SUM('🏷️ Catálogo Productos'!K2:K12)</f>
         <v>405000</v>
       </c>
       <c r="D15" s="27"/>
-      <c r="E15" s="26">
-        <f>SUM('🛒 Ventas'!H4:H60)</f>
+      <c r="E15" s="30">
+        <f>SUM('🛒 Ventas'!H2:H58)</f>
         <v>0</v>
       </c>
       <c r="F15" s="27"/>
-      <c r="G15" s="26">
-        <f>SUM('🏢 Activos Fijos'!H4:H13)</f>
+      <c r="G15" s="30">
+        <f>SUM('🏢 Activos Fijos'!H2:H11)</f>
         <v>4150000</v>
       </c>
       <c r="H15" s="27"/>
@@ -1940,6 +1928,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
@@ -1956,14 +1952,6 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1972,7 +1960,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>'🏷️ Catálogo Productos'!$A$4:$A$15</xm:f>
+            <xm:f>'🏷️ Catálogo Productos'!$A$2:$A$13</xm:f>
           </x14:formula1>
           <xm:sqref>C4</xm:sqref>
         </x14:dataValidation>
@@ -2112,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2126,72 +2114,142 @@
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-    </row>
-    <row r="3" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="B1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="14" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>66</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="8">
+        <v>25000</v>
+      </c>
+      <c r="F2" s="8">
+        <v>55000</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7">
+        <f>SUMIF('📥 Entradas'!C:C, A2, '📥 Entradas'!F:F)</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="7">
+        <f>SUMIF('🛒 Ventas'!C:C, A2, '🛒 Ventas'!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <f t="shared" ref="J2:J12" si="0">G2+H2-I2</f>
+        <v>2</v>
+      </c>
+      <c r="K2" s="8">
+        <f t="shared" ref="K2:K12" si="1">J2*E2</f>
+        <v>50000</v>
+      </c>
+      <c r="L2" s="15" t="str">
+        <f t="shared" ref="L2:L12" si="2">IF(J2&lt;=0, "❌ Agotado", IF(J2&lt;=3, "⚠️ Stock Bajo", "✅ Disponible"))</f>
+        <v>⚠️ Stock Bajo</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="18">
+        <v>25000</v>
+      </c>
+      <c r="F3" s="18">
+        <v>55000</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="H3" s="19">
+        <f>SUMIF('📥 Entradas'!C:C, A3, '📥 Entradas'!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="19">
+        <f>SUMIF('🛒 Ventas'!C:C, A3, '🛒 Ventas'!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K3" s="18">
+        <f t="shared" si="1"/>
+        <v>25000</v>
+      </c>
+      <c r="L3" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E4" s="8">
         <v>25000</v>
@@ -2204,50 +2262,50 @@
       </c>
       <c r="H4" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A4, '📥 Entradas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, A4, '🛒 Ventas'!F:F)</f>
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" ref="J4:J14" si="0">G4+H4-I4</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" ref="K4:K14" si="1">J4*E4</f>
-        <v>50000</v>
+        <f t="shared" si="1"/>
+        <v>25000</v>
       </c>
       <c r="L4" s="15" t="str">
-        <f t="shared" ref="L4:L14" si="2">IF(J4&lt;=0, "❌ Agotado", IF(J4&lt;=3, "⚠️ Stock Bajo", "✅ Disponible"))</f>
+        <f t="shared" si="2"/>
         <v>⚠️ Stock Bajo</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E5" s="18">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="F5" s="18">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="G5" s="7">
         <v>1</v>
       </c>
       <c r="H5" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A5, '📥 Entradas'!F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="19">
         <f>SUMIF('🛒 Ventas'!C:C, A5, '🛒 Ventas'!F:F)</f>
@@ -2255,11 +2313,11 @@
       </c>
       <c r="J5" s="20">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="18">
         <f t="shared" si="1"/>
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="L5" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2268,22 +2326,22 @@
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E6" s="8">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="F6" s="8">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="G6" s="7">
         <v>1</v>
@@ -2302,7 +2360,7 @@
       </c>
       <c r="K6" s="8">
         <f t="shared" si="1"/>
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="L6" s="15" t="str">
         <f t="shared" si="2"/>
@@ -2311,16 +2369,16 @@
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E7" s="18">
         <v>30000</v>
@@ -2333,7 +2391,7 @@
       </c>
       <c r="H7" s="19">
         <f>SUMIF('📥 Entradas'!C:C, A7, '📥 Entradas'!F:F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="19">
         <f>SUMIF('🛒 Ventas'!C:C, A7, '🛒 Ventas'!F:F)</f>
@@ -2341,11 +2399,11 @@
       </c>
       <c r="J7" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="L7" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2354,22 +2412,22 @@
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="8">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="F8" s="8">
-        <v>65000</v>
+        <v>85000</v>
       </c>
       <c r="G8" s="7">
         <v>1</v>
@@ -2388,7 +2446,7 @@
       </c>
       <c r="K8" s="8">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="L8" s="15" t="str">
         <f t="shared" si="2"/>
@@ -2397,22 +2455,22 @@
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E9" s="18">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="F9" s="18">
-        <v>65000</v>
+        <v>85000</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -2431,7 +2489,7 @@
       </c>
       <c r="K9" s="18">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="L9" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2440,16 +2498,16 @@
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E10" s="8">
         <v>40000</v>
@@ -2483,22 +2541,22 @@
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="18">
-        <v>40000</v>
+        <v>35000</v>
       </c>
       <c r="F11" s="18">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="G11" s="7">
         <v>1</v>
@@ -2517,7 +2575,7 @@
       </c>
       <c r="K11" s="18">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>35000</v>
       </c>
       <c r="L11" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2526,29 +2584,29 @@
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E12" s="8">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="F12" s="8">
-        <v>85000</v>
+        <v>35000</v>
       </c>
       <c r="G12" s="7">
         <v>1</v>
       </c>
       <c r="H12" s="7">
         <f>SUMIF('📥 Entradas'!C:C, A12, '📥 Entradas'!F:F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="7">
         <f>SUMIF('🛒 Ventas'!C:C, A12, '🛒 Ventas'!F:F)</f>
@@ -2556,142 +2614,53 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="8">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="L12" s="15" t="str">
         <f t="shared" si="2"/>
         <v>⚠️ Stock Bajo</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="18">
-        <v>35000</v>
-      </c>
-      <c r="F13" s="18">
-        <v>75000</v>
-      </c>
-      <c r="G13" s="7">
-        <v>1</v>
-      </c>
-      <c r="H13" s="19">
-        <f>SUMIF('📥 Entradas'!C:C, A13, '📥 Entradas'!F:F)</f>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10">
+        <f>SUM(H2:H12)</f>
+        <v>3</v>
+      </c>
+      <c r="I13" s="10">
+        <f>SUM(I2:I12)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="19">
-        <f>SUMIF('🛒 Ventas'!C:C, A13, '🛒 Ventas'!F:F)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K13" s="18">
-        <f t="shared" si="1"/>
-        <v>35000</v>
-      </c>
-      <c r="L13" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>⚠️ Stock Bajo</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="8">
-        <v>15000</v>
-      </c>
-      <c r="F14" s="8">
-        <v>35000</v>
-      </c>
-      <c r="G14" s="7">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7">
-        <f>SUMIF('📥 Entradas'!C:C, A14, '📥 Entradas'!F:F)</f>
-        <v>1</v>
-      </c>
-      <c r="I14" s="7">
-        <f>SUMIF('🛒 Ventas'!C:C, A14, '🛒 Ventas'!F:F)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="L14" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>⚠️ Stock Bajo</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10">
-        <f>SUM(H4:H14)</f>
-        <v>3</v>
-      </c>
-      <c r="I15" s="10">
-        <f>SUM(I4:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="10">
-        <f>SUM(J4:J14)</f>
+      <c r="J13" s="10">
+        <f>SUM(J2:J12)</f>
         <v>14</v>
       </c>
-      <c r="K15" s="11">
-        <f>SUM(K4:K14)</f>
+      <c r="K13" s="11">
+        <f>SUM(K2:K12)</f>
         <v>405000</v>
       </c>
-      <c r="L15" s="9"/>
+      <c r="L13" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -2703,146 +2672,183 @@
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-    </row>
-    <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="E1" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="G1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="14" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>90</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f>IFERROR(VLOOKUP(C2, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
+        <v>Top Velvet Negro</v>
+      </c>
+      <c r="E2" s="15" t="str">
+        <f>IFERROR(VLOOKUP(C2, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
+        <v>M</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8">
+        <f>IFERROR(VLOOKUP(C2, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
+        <v>25000</v>
+      </c>
+      <c r="H2" s="8">
+        <f>F2*G2</f>
+        <v>25000</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f>IFERROR(VLOOKUP(C3, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
+        <v>Short Pole Grip Talle Alto</v>
+      </c>
+      <c r="E3" s="15" t="str">
+        <f>IFERROR(VLOOKUP(C3, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
+        <v>M</v>
+      </c>
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8">
+        <f>IFERROR(VLOOKUP(C3, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
+        <v>30000</v>
+      </c>
+      <c r="H3" s="8">
+        <f>F3*G3</f>
+        <v>30000</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="D4" s="6" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Top Velvet Negro</v>
+        <v>Grip Pole Tacky Gel 50ml</v>
       </c>
       <c r="E4" s="15" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>M</v>
+        <v>Única</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
       </c>
       <c r="G4" s="8">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="H4" s="8">
         <f>F4*G4</f>
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>70</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="6" t="str">
-        <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Short Pole Grip Talle Alto</v>
+        <f>IFERROR(IF(C5="","",VLOOKUP(C5, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
+        <v/>
       </c>
       <c r="E5" s="15" t="str">
-        <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>M</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8">
-        <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
-        <v>30000</v>
-      </c>
-      <c r="H5" s="8">
-        <f>F5*G5</f>
-        <v>30000</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>93</v>
-      </c>
+        <f>IFERROR(IF(C5="","",VLOOKUP(C5, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="22" t="str">
+        <f>IFERROR(IF(C5="","",VLOOKUP(C5, '🏷️ Catálogo Productos'!A:E, 5, FALSE)), 0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="22" t="str">
+        <f t="shared" ref="H5:H27" si="0">IF(F5="","",F5*G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>80</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Grip Pole Tacky Gel 50ml</v>
+        <f>IFERROR(IF(C6="","",VLOOKUP(C6, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
+        <v/>
       </c>
       <c r="E6" s="15" t="str">
-        <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>Única</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:E, 5, FALSE), 0)</f>
-        <v>15000</v>
-      </c>
-      <c r="H6" s="8">
-        <f>F6*G6</f>
-        <v>15000</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>97</v>
-      </c>
+        <f>IFERROR(IF(C6="","",VLOOKUP(C6, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="22" t="str">
+        <f>IFERROR(IF(C6="","",VLOOKUP(C6, '🏷️ Catálogo Productos'!A:E, 5, FALSE)), 0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
@@ -2864,7 +2870,7 @@
         <v/>
       </c>
       <c r="H7" s="22" t="str">
-        <f t="shared" ref="H7:H29" si="0">IF(F7="","",F7*G7)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I7" s="1"/>
@@ -3369,69 +3375,16 @@
       </c>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="6" t="str">
-        <f>IFERROR(IF(C28="","",VLOOKUP(C28, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="E28" s="15" t="str">
-        <f>IFERROR(IF(C28="","",VLOOKUP(C28, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="22" t="str">
-        <f>IFERROR(IF(C28="","",VLOOKUP(C28, '🏷️ Catálogo Productos'!A:E, 5, FALSE)), 0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="6" t="str">
-        <f>IFERROR(IF(C29="","",VLOOKUP(C29, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="E29" s="15" t="str">
-        <f>IFERROR(IF(C29="","",VLOOKUP(C29, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="22" t="str">
-        <f>IFERROR(IF(C29="","",VLOOKUP(C29, '🏷️ Catálogo Productos'!A:E, 5, FALSE)), 0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I29" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
-            <xm:f>'🏷️ Catálogo Productos'!$A$4:$A$15</xm:f>
+            <xm:f>'🏷️ Catálogo Productos'!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>C4:C30 C4:C60</xm:sqref>
+          <xm:sqref>C2:C58</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3441,7 +3394,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3455,82 +3408,138 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-    </row>
-    <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="I1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="14" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="str">
+        <f>IF(C2="","", C2 &amp; COUNTIF($C$2:C2, C2))</f>
+        <v>TM1</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="C2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f>IFERROR(VLOOKUP(C2, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
+        <v>Top Velvet Negro</v>
+      </c>
+      <c r="E2" s="15" t="str">
+        <f>IFERROR(VLOOKUP(C2, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
+        <v>M</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8">
+        <f>IFERROR(VLOOKUP(C2, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
+        <v>55000</v>
+      </c>
+      <c r="H2" s="8">
+        <f>F2*G2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="14" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="str">
+        <f>IF(C3="","", C3 &amp; COUNTIF($C$2:C3, C3))</f>
+        <v>SM1</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>127</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f>IFERROR(VLOOKUP(C3, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
+        <v>Short Pole Grip Talle Alto</v>
+      </c>
+      <c r="E3" s="15" t="str">
+        <f>IFERROR(VLOOKUP(C3, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
+        <v>M</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8">
+        <f>IFERROR(VLOOKUP(C3, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
+        <v>65000</v>
+      </c>
+      <c r="H3" s="8">
+        <f>F3*G3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="str">
-        <f>IF(C4="","", C4 &amp; COUNTIF($C$4:C4, C4))</f>
-        <v>TM1</v>
+        <f>IF(C4="","", C4 &amp; COUNTIF($C$2:C4, C4))</f>
+        <v>PS1</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>128</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="D4" s="6" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Top Velvet Negro</v>
+        <v>Pantalón Lycra Flare Studio</v>
       </c>
       <c r="E4" s="15" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
-        <v>55000</v>
+        <v>85000</v>
       </c>
       <c r="H4" s="8">
         <f>F4*G4</f>
         <v>0</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>129</v>
@@ -3538,147 +3547,131 @@
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="str">
-        <f>IF(C5="","", C5 &amp; COUNTIF($C$4:C5, C5))</f>
-        <v>SM1</v>
+        <f>IF(C5="","", C5 &amp; COUNTIF($C$2:C5, C5))</f>
+        <v>AU1</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>130</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D5" s="6" t="str">
         <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Short Pole Grip Talle Alto</v>
+        <v>Grip Pole Tacky Gel 50ml</v>
       </c>
       <c r="E5" s="15" t="str">
         <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>M</v>
+        <v>Única</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="8">
         <f>IFERROR(VLOOKUP(C5, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
-        <v>65000</v>
+        <v>35000</v>
       </c>
       <c r="H5" s="8">
         <f>F5*G5</f>
         <v>0</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="str">
-        <f>IF(C6="","", C6 &amp; COUNTIF($C$4:C6, C6))</f>
-        <v>PS1</v>
+        <f>IF(C6="","", C6 &amp; COUNTIF($C$2:C6, C6))</f>
+        <v>TM2</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Pantalón Lycra Flare Studio</v>
+        <v>Top Velvet Negro</v>
       </c>
       <c r="E6" s="15" t="str">
         <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="8">
         <f>IFERROR(VLOOKUP(C6, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
-        <v>85000</v>
+        <v>55000</v>
       </c>
       <c r="H6" s="8">
         <f>F6*G6</f>
         <v>0</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="str">
-        <f>IF(C7="","", C7 &amp; COUNTIF($C$4:C7, C7))</f>
-        <v>AU1</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>80</v>
-      </c>
+        <f>IF(C7="","", C7 &amp; COUNTIF($C$2:C7, C7))</f>
+        <v/>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
       <c r="D7" s="6" t="str">
-        <f>IFERROR(VLOOKUP(C7, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Grip Pole Tacky Gel 50ml</v>
+        <f>IFERROR(IF(C7="","",VLOOKUP(C7, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
+        <v/>
       </c>
       <c r="E7" s="15" t="str">
-        <f>IFERROR(VLOOKUP(C7, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>Única</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8">
-        <f>IFERROR(VLOOKUP(C7, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
-        <v>35000</v>
-      </c>
-      <c r="H7" s="8">
-        <f>F7*G7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>129</v>
-      </c>
+        <f>IFERROR(IF(C7="","",VLOOKUP(C7, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="22" t="str">
+        <f>IFERROR(IF(C7="","",VLOOKUP(C7, '🏷️ Catálogo Productos'!A:F, 6, FALSE)), 0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="22" t="str">
+        <f t="shared" ref="H7:H38" si="0">IF(F7="","",F7*G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="str">
-        <f>IF(C8="","", C8 &amp; COUNTIF($C$4:C8, C8))</f>
-        <v>TM2</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>3</v>
-      </c>
+        <f>IF(C8="","", C8 &amp; COUNTIF($C$2:C8, C8))</f>
+        <v/>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
       <c r="D8" s="6" t="str">
-        <f>IFERROR(VLOOKUP(C8, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "")</f>
-        <v>Top Velvet Negro</v>
+        <f>IFERROR(IF(C8="","",VLOOKUP(C8, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
+        <v/>
       </c>
       <c r="E8" s="15" t="str">
-        <f>IFERROR(VLOOKUP(C8, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "")</f>
-        <v>M</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8">
-        <f>IFERROR(VLOOKUP(C8, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
-        <v>55000</v>
-      </c>
-      <c r="H8" s="8">
-        <f>F8*G8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>129</v>
-      </c>
+        <f>IFERROR(IF(C8="","",VLOOKUP(C8, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="22" t="str">
+        <f>IFERROR(IF(C8="","",VLOOKUP(C8, '🏷️ Catálogo Productos'!A:F, 6, FALSE)), 0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="str">
-        <f>IF(C9="","", C9 &amp; COUNTIF($C$4:C9, C9))</f>
+        <f>IF(C9="","", C9 &amp; COUNTIF($C$2:C9, C9))</f>
         <v/>
       </c>
       <c r="B9" s="1"/>
@@ -3697,7 +3690,7 @@
         <v/>
       </c>
       <c r="H9" s="22" t="str">
-        <f t="shared" ref="H9:H40" si="0">IF(F9="","",F9*G9)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I9" s="1"/>
@@ -3705,7 +3698,7 @@
     </row>
     <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="str">
-        <f>IF(C10="","", C10 &amp; COUNTIF($C$4:C10, C10))</f>
+        <f>IF(C10="","", C10 &amp; COUNTIF($C$2:C10, C10))</f>
         <v/>
       </c>
       <c r="B10" s="1"/>
@@ -3732,7 +3725,7 @@
     </row>
     <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="str">
-        <f>IF(C11="","", C11 &amp; COUNTIF($C$4:C11, C11))</f>
+        <f>IF(C11="","", C11 &amp; COUNTIF($C$2:C11, C11))</f>
         <v/>
       </c>
       <c r="B11" s="1"/>
@@ -3759,7 +3752,7 @@
     </row>
     <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="str">
-        <f>IF(C12="","", C12 &amp; COUNTIF($C$4:C12, C12))</f>
+        <f>IF(C12="","", C12 &amp; COUNTIF($C$2:C12, C12))</f>
         <v/>
       </c>
       <c r="B12" s="1"/>
@@ -3786,7 +3779,7 @@
     </row>
     <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="str">
-        <f>IF(C13="","", C13 &amp; COUNTIF($C$4:C13, C13))</f>
+        <f>IF(C13="","", C13 &amp; COUNTIF($C$2:C13, C13))</f>
         <v/>
       </c>
       <c r="B13" s="1"/>
@@ -3813,7 +3806,7 @@
     </row>
     <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="str">
-        <f>IF(C14="","", C14 &amp; COUNTIF($C$4:C14, C14))</f>
+        <f>IF(C14="","", C14 &amp; COUNTIF($C$2:C14, C14))</f>
         <v/>
       </c>
       <c r="B14" s="1"/>
@@ -3840,7 +3833,7 @@
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="str">
-        <f>IF(C15="","", C15 &amp; COUNTIF($C$4:C15, C15))</f>
+        <f>IF(C15="","", C15 &amp; COUNTIF($C$2:C15, C15))</f>
         <v/>
       </c>
       <c r="B15" s="1"/>
@@ -3867,7 +3860,7 @@
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="str">
-        <f>IF(C16="","", C16 &amp; COUNTIF($C$4:C16, C16))</f>
+        <f>IF(C16="","", C16 &amp; COUNTIF($C$2:C16, C16))</f>
         <v/>
       </c>
       <c r="B16" s="1"/>
@@ -3894,7 +3887,7 @@
     </row>
     <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="str">
-        <f>IF(C17="","", C17 &amp; COUNTIF($C$4:C17, C17))</f>
+        <f>IF(C17="","", C17 &amp; COUNTIF($C$2:C17, C17))</f>
         <v/>
       </c>
       <c r="B17" s="1"/>
@@ -3921,7 +3914,7 @@
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="str">
-        <f>IF(C18="","", C18 &amp; COUNTIF($C$4:C18, C18))</f>
+        <f>IF(C18="","", C18 &amp; COUNTIF($C$2:C18, C18))</f>
         <v/>
       </c>
       <c r="B18" s="1"/>
@@ -3948,7 +3941,7 @@
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="str">
-        <f>IF(C19="","", C19 &amp; COUNTIF($C$4:C19, C19))</f>
+        <f>IF(C19="","", C19 &amp; COUNTIF($C$2:C19, C19))</f>
         <v/>
       </c>
       <c r="B19" s="1"/>
@@ -3975,7 +3968,7 @@
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="str">
-        <f>IF(C20="","", C20 &amp; COUNTIF($C$4:C20, C20))</f>
+        <f>IF(C20="","", C20 &amp; COUNTIF($C$2:C20, C20))</f>
         <v/>
       </c>
       <c r="B20" s="1"/>
@@ -4002,7 +3995,7 @@
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="str">
-        <f>IF(C21="","", C21 &amp; COUNTIF($C$4:C21, C21))</f>
+        <f>IF(C21="","", C21 &amp; COUNTIF($C$2:C21, C21))</f>
         <v/>
       </c>
       <c r="B21" s="1"/>
@@ -4029,7 +4022,7 @@
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="str">
-        <f>IF(C22="","", C22 &amp; COUNTIF($C$4:C22, C22))</f>
+        <f>IF(C22="","", C22 &amp; COUNTIF($C$2:C22, C22))</f>
         <v/>
       </c>
       <c r="B22" s="1"/>
@@ -4056,7 +4049,7 @@
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="str">
-        <f>IF(C23="","", C23 &amp; COUNTIF($C$4:C23, C23))</f>
+        <f>IF(C23="","", C23 &amp; COUNTIF($C$2:C23, C23))</f>
         <v/>
       </c>
       <c r="B23" s="1"/>
@@ -4083,7 +4076,7 @@
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="str">
-        <f>IF(C24="","", C24 &amp; COUNTIF($C$4:C24, C24))</f>
+        <f>IF(C24="","", C24 &amp; COUNTIF($C$2:C24, C24))</f>
         <v/>
       </c>
       <c r="B24" s="1"/>
@@ -4110,7 +4103,7 @@
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="str">
-        <f>IF(C25="","", C25 &amp; COUNTIF($C$4:C25, C25))</f>
+        <f>IF(C25="","", C25 &amp; COUNTIF($C$2:C25, C25))</f>
         <v/>
       </c>
       <c r="B25" s="1"/>
@@ -4137,7 +4130,7 @@
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="str">
-        <f>IF(C26="","", C26 &amp; COUNTIF($C$4:C26, C26))</f>
+        <f>IF(C26="","", C26 &amp; COUNTIF($C$2:C26, C26))</f>
         <v/>
       </c>
       <c r="B26" s="1"/>
@@ -4164,7 +4157,7 @@
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="str">
-        <f>IF(C27="","", C27 &amp; COUNTIF($C$4:C27, C27))</f>
+        <f>IF(C27="","", C27 &amp; COUNTIF($C$2:C27, C27))</f>
         <v/>
       </c>
       <c r="B27" s="1"/>
@@ -4191,7 +4184,7 @@
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="str">
-        <f>IF(C28="","", C28 &amp; COUNTIF($C$4:C28, C28))</f>
+        <f>IF(C28="","", C28 &amp; COUNTIF($C$2:C28, C28))</f>
         <v/>
       </c>
       <c r="B28" s="1"/>
@@ -4218,7 +4211,7 @@
     </row>
     <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="str">
-        <f>IF(C29="","", C29 &amp; COUNTIF($C$4:C29, C29))</f>
+        <f>IF(C29="","", C29 &amp; COUNTIF($C$2:C29, C29))</f>
         <v/>
       </c>
       <c r="B29" s="1"/>
@@ -4245,7 +4238,7 @@
     </row>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="str">
-        <f>IF(C30="","", C30 &amp; COUNTIF($C$4:C30, C30))</f>
+        <f>IF(C30="","", C30 &amp; COUNTIF($C$2:C30, C30))</f>
         <v/>
       </c>
       <c r="B30" s="1"/>
@@ -4272,7 +4265,7 @@
     </row>
     <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="str">
-        <f>IF(C31="","", C31 &amp; COUNTIF($C$4:C31, C31))</f>
+        <f>IF(C31="","", C31 &amp; COUNTIF($C$2:C31, C31))</f>
         <v/>
       </c>
       <c r="B31" s="1"/>
@@ -4299,7 +4292,7 @@
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="str">
-        <f>IF(C32="","", C32 &amp; COUNTIF($C$4:C32, C32))</f>
+        <f>IF(C32="","", C32 &amp; COUNTIF($C$2:C32, C32))</f>
         <v/>
       </c>
       <c r="B32" s="1"/>
@@ -4326,7 +4319,7 @@
     </row>
     <row r="33" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="str">
-        <f>IF(C33="","", C33 &amp; COUNTIF($C$4:C33, C33))</f>
+        <f>IF(C33="","", C33 &amp; COUNTIF($C$2:C33, C33))</f>
         <v/>
       </c>
       <c r="B33" s="1"/>
@@ -4353,7 +4346,7 @@
     </row>
     <row r="34" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="str">
-        <f>IF(C34="","", C34 &amp; COUNTIF($C$4:C34, C34))</f>
+        <f>IF(C34="","", C34 &amp; COUNTIF($C$2:C34, C34))</f>
         <v/>
       </c>
       <c r="B34" s="1"/>
@@ -4380,7 +4373,7 @@
     </row>
     <row r="35" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="str">
-        <f>IF(C35="","", C35 &amp; COUNTIF($C$4:C35, C35))</f>
+        <f>IF(C35="","", C35 &amp; COUNTIF($C$2:C35, C35))</f>
         <v/>
       </c>
       <c r="B35" s="1"/>
@@ -4407,7 +4400,7 @@
     </row>
     <row r="36" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="str">
-        <f>IF(C36="","", C36 &amp; COUNTIF($C$4:C36, C36))</f>
+        <f>IF(C36="","", C36 &amp; COUNTIF($C$2:C36, C36))</f>
         <v/>
       </c>
       <c r="B36" s="1"/>
@@ -4434,7 +4427,7 @@
     </row>
     <row r="37" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="str">
-        <f>IF(C37="","", C37 &amp; COUNTIF($C$4:C37, C37))</f>
+        <f>IF(C37="","", C37 &amp; COUNTIF($C$2:C37, C37))</f>
         <v/>
       </c>
       <c r="B37" s="1"/>
@@ -4461,7 +4454,7 @@
     </row>
     <row r="38" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="str">
-        <f>IF(C38="","", C38 &amp; COUNTIF($C$4:C38, C38))</f>
+        <f>IF(C38="","", C38 &amp; COUNTIF($C$2:C38, C38))</f>
         <v/>
       </c>
       <c r="B38" s="1"/>
@@ -4488,7 +4481,7 @@
     </row>
     <row r="39" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="str">
-        <f>IF(C39="","", C39 &amp; COUNTIF($C$4:C39, C39))</f>
+        <f>IF(C39="","", C39 &amp; COUNTIF($C$2:C39, C39))</f>
         <v/>
       </c>
       <c r="B39" s="1"/>
@@ -4507,7 +4500,7 @@
         <v/>
       </c>
       <c r="H39" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H39:H57" si="1">IF(F39="","",F39*G39)</f>
         <v/>
       </c>
       <c r="I39" s="1"/>
@@ -4515,7 +4508,7 @@
     </row>
     <row r="40" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="str">
-        <f>IF(C40="","", C40 &amp; COUNTIF($C$4:C40, C40))</f>
+        <f>IF(C40="","", C40 &amp; COUNTIF($C$2:C40, C40))</f>
         <v/>
       </c>
       <c r="B40" s="1"/>
@@ -4534,7 +4527,7 @@
         <v/>
       </c>
       <c r="H40" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I40" s="1"/>
@@ -4542,7 +4535,7 @@
     </row>
     <row r="41" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="str">
-        <f>IF(C41="","", C41 &amp; COUNTIF($C$4:C41, C41))</f>
+        <f>IF(C41="","", C41 &amp; COUNTIF($C$2:C41, C41))</f>
         <v/>
       </c>
       <c r="B41" s="1"/>
@@ -4561,7 +4554,7 @@
         <v/>
       </c>
       <c r="H41" s="22" t="str">
-        <f t="shared" ref="H41:H59" si="1">IF(F41="","",F41*G41)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I41" s="1"/>
@@ -4569,7 +4562,7 @@
     </row>
     <row r="42" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="str">
-        <f>IF(C42="","", C42 &amp; COUNTIF($C$4:C42, C42))</f>
+        <f>IF(C42="","", C42 &amp; COUNTIF($C$2:C42, C42))</f>
         <v/>
       </c>
       <c r="B42" s="1"/>
@@ -4596,7 +4589,7 @@
     </row>
     <row r="43" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="str">
-        <f>IF(C43="","", C43 &amp; COUNTIF($C$4:C43, C43))</f>
+        <f>IF(C43="","", C43 &amp; COUNTIF($C$2:C43, C43))</f>
         <v/>
       </c>
       <c r="B43" s="1"/>
@@ -4623,7 +4616,7 @@
     </row>
     <row r="44" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="str">
-        <f>IF(C44="","", C44 &amp; COUNTIF($C$4:C44, C44))</f>
+        <f>IF(C44="","", C44 &amp; COUNTIF($C$2:C44, C44))</f>
         <v/>
       </c>
       <c r="B44" s="1"/>
@@ -4650,7 +4643,7 @@
     </row>
     <row r="45" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="str">
-        <f>IF(C45="","", C45 &amp; COUNTIF($C$4:C45, C45))</f>
+        <f>IF(C45="","", C45 &amp; COUNTIF($C$2:C45, C45))</f>
         <v/>
       </c>
       <c r="B45" s="1"/>
@@ -4677,7 +4670,7 @@
     </row>
     <row r="46" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="str">
-        <f>IF(C46="","", C46 &amp; COUNTIF($C$4:C46, C46))</f>
+        <f>IF(C46="","", C46 &amp; COUNTIF($C$2:C46, C46))</f>
         <v/>
       </c>
       <c r="B46" s="1"/>
@@ -4704,7 +4697,7 @@
     </row>
     <row r="47" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="str">
-        <f>IF(C47="","", C47 &amp; COUNTIF($C$4:C47, C47))</f>
+        <f>IF(C47="","", C47 &amp; COUNTIF($C$2:C47, C47))</f>
         <v/>
       </c>
       <c r="B47" s="1"/>
@@ -4731,7 +4724,7 @@
     </row>
     <row r="48" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="str">
-        <f>IF(C48="","", C48 &amp; COUNTIF($C$4:C48, C48))</f>
+        <f>IF(C48="","", C48 &amp; COUNTIF($C$2:C48, C48))</f>
         <v/>
       </c>
       <c r="B48" s="1"/>
@@ -4758,7 +4751,7 @@
     </row>
     <row r="49" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="str">
-        <f>IF(C49="","", C49 &amp; COUNTIF($C$4:C49, C49))</f>
+        <f>IF(C49="","", C49 &amp; COUNTIF($C$2:C49, C49))</f>
         <v/>
       </c>
       <c r="B49" s="1"/>
@@ -4785,7 +4778,7 @@
     </row>
     <row r="50" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="str">
-        <f>IF(C50="","", C50 &amp; COUNTIF($C$4:C50, C50))</f>
+        <f>IF(C50="","", C50 &amp; COUNTIF($C$2:C50, C50))</f>
         <v/>
       </c>
       <c r="B50" s="1"/>
@@ -4812,7 +4805,7 @@
     </row>
     <row r="51" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="str">
-        <f>IF(C51="","", C51 &amp; COUNTIF($C$4:C51, C51))</f>
+        <f>IF(C51="","", C51 &amp; COUNTIF($C$2:C51, C51))</f>
         <v/>
       </c>
       <c r="B51" s="1"/>
@@ -4839,7 +4832,7 @@
     </row>
     <row r="52" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="str">
-        <f>IF(C52="","", C52 &amp; COUNTIF($C$4:C52, C52))</f>
+        <f>IF(C52="","", C52 &amp; COUNTIF($C$2:C52, C52))</f>
         <v/>
       </c>
       <c r="B52" s="1"/>
@@ -4866,7 +4859,7 @@
     </row>
     <row r="53" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="str">
-        <f>IF(C53="","", C53 &amp; COUNTIF($C$4:C53, C53))</f>
+        <f>IF(C53="","", C53 &amp; COUNTIF($C$2:C53, C53))</f>
         <v/>
       </c>
       <c r="B53" s="1"/>
@@ -4893,7 +4886,7 @@
     </row>
     <row r="54" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="str">
-        <f>IF(C54="","", C54 &amp; COUNTIF($C$4:C54, C54))</f>
+        <f>IF(C54="","", C54 &amp; COUNTIF($C$2:C54, C54))</f>
         <v/>
       </c>
       <c r="B54" s="1"/>
@@ -4920,7 +4913,7 @@
     </row>
     <row r="55" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="str">
-        <f>IF(C55="","", C55 &amp; COUNTIF($C$4:C55, C55))</f>
+        <f>IF(C55="","", C55 &amp; COUNTIF($C$2:C55, C55))</f>
         <v/>
       </c>
       <c r="B55" s="1"/>
@@ -4947,7 +4940,7 @@
     </row>
     <row r="56" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="str">
-        <f>IF(C56="","", C56 &amp; COUNTIF($C$4:C56, C56))</f>
+        <f>IF(C56="","", C56 &amp; COUNTIF($C$2:C56, C56))</f>
         <v/>
       </c>
       <c r="B56" s="1"/>
@@ -4974,7 +4967,7 @@
     </row>
     <row r="57" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="str">
-        <f>IF(C57="","", C57 &amp; COUNTIF($C$4:C57, C57))</f>
+        <f>IF(C57="","", C57 &amp; COUNTIF($C$2:C57, C57))</f>
         <v/>
       </c>
       <c r="B57" s="1"/>
@@ -4999,79 +4992,22 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="str">
-        <f>IF(C58="","", C58 &amp; COUNTIF($C$4:C58, C58))</f>
-        <v/>
-      </c>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="6" t="str">
-        <f>IFERROR(IF(C58="","",VLOOKUP(C58, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="E58" s="15" t="str">
-        <f>IFERROR(IF(C58="","",VLOOKUP(C58, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="22" t="str">
-        <f>IFERROR(IF(C58="","",VLOOKUP(C58, '🏷️ Catálogo Productos'!A:F, 6, FALSE)), 0)</f>
-        <v/>
-      </c>
-      <c r="H58" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="str">
-        <f>IF(C59="","", C59 &amp; COUNTIF($C$4:C59, C59))</f>
-        <v/>
-      </c>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="6" t="str">
-        <f>IFERROR(IF(C59="","",VLOOKUP(C59, '🏷️ Catálogo Productos'!A:C, 3, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="E59" s="15" t="str">
-        <f>IFERROR(IF(C59="","",VLOOKUP(C59, '🏷️ Catálogo Productos'!A:D, 4, FALSE)), "")</f>
-        <v/>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="22" t="str">
-        <f>IFERROR(IF(C59="","",VLOOKUP(C59, '🏷️ Catálogo Productos'!A:F, 6, FALSE)), 0)</f>
-        <v/>
-      </c>
-      <c r="H59" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0400-000000000000}">
           <x14:formula1>
-            <xm:f>'🏷️ Catálogo Productos'!$A$4:$A$15</xm:f>
+            <xm:f>'🏷️ Catálogo Productos'!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>C4:C30 C4:C60</xm:sqref>
+          <xm:sqref>C2:C58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$E$4:$E$8</xm:f>
           </x14:formula1>
-          <xm:sqref>I4:I60</xm:sqref>
+          <xm:sqref>I2:I58</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5081,7 +5017,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -5096,100 +5032,152 @@
     <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-    </row>
-    <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G3" s="14" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="B2" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="E2" s="7">
+        <v>2</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="8">
+        <v>1200000</v>
+      </c>
+      <c r="H2" s="8">
+        <f t="shared" ref="H2:H3" si="0">E2*G2</f>
+        <v>2400000</v>
+      </c>
+      <c r="I2" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J2" s="6" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="19">
+        <v>3</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="18">
+        <v>350000</v>
+      </c>
+      <c r="H3" s="18">
+        <f t="shared" si="0"/>
+        <v>1050000</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
+      <c r="D4" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="19">
+        <v>1</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="8">
-        <v>1200000</v>
-      </c>
-      <c r="H4" s="8">
-        <f t="shared" ref="H4:H5" si="0">E4*G4</f>
-        <v>2400000</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>148</v>
+      <c r="G4" s="18">
+        <v>350000</v>
+      </c>
+      <c r="H4" s="18">
+        <f t="shared" ref="H4" si="1">E4*G4</f>
+        <v>350000</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>195</v>
+        <v>152</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E5" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>41</v>
@@ -5198,271 +5186,233 @@
         <v>350000</v>
       </c>
       <c r="H5" s="18">
-        <f t="shared" si="0"/>
-        <v>1050000</v>
+        <f t="shared" ref="H5" si="2">E5*G5</f>
+        <v>350000</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="19">
-        <v>1</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="7"/>
       <c r="F6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="18">
-        <v>350000</v>
-      </c>
-      <c r="H6" s="18">
-        <f t="shared" ref="H6" si="1">E6*G6</f>
-        <v>350000</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="J6" s="17" t="s">
+      <c r="G6" s="8">
+        <v>15000</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" ref="H6:H11" si="3">E6*G6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>150</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="19">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="E7" s="19"/>
       <c r="F7" s="15" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="18">
-        <v>350000</v>
+        <v>45000</v>
       </c>
       <c r="H7" s="18">
-        <f t="shared" ref="H7" si="2">E7*G7</f>
-        <v>350000</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="15" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="8">
-        <v>15000</v>
+        <v>60000</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" ref="H8:H13" si="3">E8*G8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="15" t="s">
         <v>41</v>
       </c>
       <c r="G9" s="18">
-        <v>45000</v>
+        <v>450000</v>
       </c>
       <c r="H9" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>169</v>
+      <c r="A10" s="16" t="s">
+        <v>190</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="15" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="8">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>174</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="15" t="s">
         <v>41</v>
       </c>
       <c r="G11" s="18">
-        <v>450000</v>
+        <v>850000</v>
       </c>
       <c r="H11" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="8">
-        <v>80000</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>173</v>
-      </c>
+      <c r="A12" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>146</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
       <c r="E13" s="19"/>
-      <c r="F13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="18">
-        <v>850000</v>
-      </c>
-      <c r="H13" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>176</v>
-      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -5476,7 +5426,7 @@
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -5490,7 +5440,7 @@
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -5504,7 +5454,7 @@
     </row>
     <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -5518,7 +5468,7 @@
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -5532,76 +5482,82 @@
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="16"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H19" s="16"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" s="10">
+        <f>SUM(E2:E11)</f>
+        <v>7</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="11">
+        <f>SUM(H2:H11)</f>
+        <v>4150000</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="23"/>
-    </row>
-    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="22" t="str">
+        <f t="shared" ref="H22:H35" si="4">IF(E22="","",E22*G22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="15" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
         <v>187</v>
-      </c>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="1:10" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="E23" s="10">
-        <f>SUM(E4:E13)</f>
-        <v>7</v>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="11">
-        <f>SUM(H4:H13)</f>
-        <v>4150000</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
-        <v>189</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5610,7 +5566,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="22" t="str">
-        <f t="shared" ref="H24:H37" si="4">IF(E24="","",E24*G24)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I24" s="1"/>
@@ -5618,7 +5574,7 @@
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5635,7 +5591,7 @@
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5652,7 +5608,7 @@
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5669,7 +5625,7 @@
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5686,7 +5642,7 @@
     </row>
     <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5703,7 +5659,7 @@
     </row>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5720,7 +5676,7 @@
     </row>
     <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5737,7 +5693,7 @@
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5754,7 +5710,7 @@
     </row>
     <row r="33" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5771,7 +5727,7 @@
     </row>
     <row r="34" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5786,9 +5742,9 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -5801,45 +5757,8 @@
         <v/>
       </c>
       <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I37" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -5849,13 +5768,13 @@
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$I$4:$I$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C23:C41 B21 C4:C20</xm:sqref>
+          <xm:sqref>C21:C39 B19 C2:C18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$G$4:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F23:F41 E21 F4:F20</xm:sqref>
+          <xm:sqref>F21:F39 E19 F2:F18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Control_Inventario_Pole_Dance.xlsx
+++ b/Control_Inventario_Pole_Dance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cenicanaoff365-my.sharepoint.com/personal/iavar3_cenicanaoff365_onmicrosoft_com/Documents/Escritorio/Academia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A9FECFD-AF0B-4891-848D-55B74A6FD964}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF19AC0-A734-464B-A63B-8D632686E1F6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="193">
   <si>
     <t>PANEL DE CONTROL E INVENTARIOS - POLE DANCE ACADEMY</t>
   </si>
@@ -563,12 +563,6 @@
   </si>
   <si>
     <t>ACT-010</t>
-  </si>
-  <si>
-    <t>ACT-011</t>
-  </si>
-  <si>
-    <t>ACT-012</t>
   </si>
   <si>
     <t>ACT-013</t>
@@ -780,7 +774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -834,30 +828,30 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -867,9 +861,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1603,101 +1594,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="27"/>
+      <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="36" t="str">
+      <c r="B5" s="24"/>
+      <c r="C5" s="28" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "⚠️ Código no encontrado")</f>
         <v>Top Velvet Negro</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="24"/>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="36" t="str">
+      <c r="B6" s="24"/>
+      <c r="C6" s="28" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "-")</f>
         <v>M</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="33">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>55000</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="32">
+      <c r="B8" s="24"/>
+      <c r="C8" s="26">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:J, 10, FALSE), 0)</f>
         <v>2</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="24"/>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="32">
+      <c r="B9" s="24"/>
+      <c r="C9" s="26">
         <f>SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="35" t="str">
         <f>IF(C4="","", C4 &amp; (SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F) + 1))</f>
         <v>TM1</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="24"/>
     </row>
     <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
@@ -1705,54 +1696,54 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="31" t="s">
+      <c r="D14" s="24"/>
+      <c r="E14" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="31" t="s">
+      <c r="F14" s="24"/>
+      <c r="G14" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="27"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="29">
+      <c r="A15" s="32">
         <f>SUM('🏷️ Catálogo Productos'!J2:J12)</f>
         <v>14</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="30">
+      <c r="B15" s="24"/>
+      <c r="C15" s="23">
         <f>SUM('🏷️ Catálogo Productos'!K2:K12)</f>
         <v>405000</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="30">
+      <c r="D15" s="24"/>
+      <c r="E15" s="23">
         <f>SUM('🛒 Ventas'!H2:H58)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="30">
+      <c r="F15" s="24"/>
+      <c r="G15" s="23">
         <f>SUM('🏢 Activos Fijos'!H2:H11)</f>
-        <v>4150000</v>
-      </c>
-      <c r="H15" s="27"/>
+        <v>5650000</v>
+      </c>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
@@ -1928,14 +1919,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
@@ -1952,6 +1935,14 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5017,7 +5008,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -5069,7 +5060,7 @@
         <v>141</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>42</v>
@@ -5102,7 +5093,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>42</v>
@@ -5135,7 +5126,7 @@
         <v>147</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>42</v>
@@ -5168,7 +5159,7 @@
         <v>152</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>42</v>
@@ -5193,7 +5184,7 @@
         <v>143</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -5209,7 +5200,9 @@
       <c r="D6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
       <c r="F6" s="15" t="s">
         <v>41</v>
       </c>
@@ -5218,7 +5211,7 @@
       </c>
       <c r="H6" s="8">
         <f t="shared" ref="H6:H11" si="3">E6*G6</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>150</v>
@@ -5240,7 +5233,9 @@
       <c r="D7" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E7" s="19"/>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
       <c r="F7" s="15" t="s">
         <v>41</v>
       </c>
@@ -5249,7 +5244,7 @@
       </c>
       <c r="H7" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>155</v>
@@ -5271,7 +5266,9 @@
       <c r="D8" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="19">
+        <v>1</v>
+      </c>
       <c r="F8" s="15" t="s">
         <v>41</v>
       </c>
@@ -5280,7 +5277,7 @@
       </c>
       <c r="H8" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>159</v>
@@ -5302,7 +5299,9 @@
       <c r="D9" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="19"/>
+      <c r="E9" s="19">
+        <v>1</v>
+      </c>
       <c r="F9" s="15" t="s">
         <v>41</v>
       </c>
@@ -5311,7 +5310,7 @@
       </c>
       <c r="H9" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>163</v>
@@ -5322,7 +5321,7 @@
     </row>
     <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>166</v>
@@ -5333,7 +5332,9 @@
       <c r="D10" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="19">
+        <v>1</v>
+      </c>
       <c r="F10" s="15" t="s">
         <v>41</v>
       </c>
@@ -5342,7 +5343,7 @@
       </c>
       <c r="H10" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>168</v>
@@ -5356,7 +5357,7 @@
         <v>174</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>53</v>
@@ -5364,7 +5365,9 @@
       <c r="D11" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="19">
+        <v>1</v>
+      </c>
       <c r="F11" s="15" t="s">
         <v>41</v>
       </c>
@@ -5373,7 +5376,7 @@
       </c>
       <c r="H11" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>171</v>
@@ -5382,148 +5385,184 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="10">
+        <f>SUM(E2:E11)</f>
+        <v>13</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="11">
+        <f>SUM(H2:H11)</f>
+        <v>5650000</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="23"/>
+        <v>183</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="22" t="str">
+        <f t="shared" ref="H13:H26" si="4">IF(E13="","",E13*G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="23"/>
+        <v>184</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="23"/>
+        <v>185</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="23"/>
+        <v>175</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="23"/>
+        <v>176</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="23"/>
+        <v>177</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>178</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="1:10" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="10">
-        <f>SUM(E2:E11)</f>
-        <v>7</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="11">
-        <f>SUM(H2:H11)</f>
-        <v>4150000</v>
-      </c>
-      <c r="I21" s="9"/>
+        <v>180</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5532,7 +5571,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="22" t="str">
-        <f t="shared" ref="H22:H35" si="4">IF(E22="","",E22*G22)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I22" s="1"/>
@@ -5540,7 +5579,7 @@
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5557,7 +5596,7 @@
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5574,7 +5613,7 @@
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5589,9 +5628,9 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5604,159 +5643,6 @@
         <v/>
       </c>
       <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I35" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -5768,13 +5654,13 @@
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$I$4:$I$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C21:C39 B19 C2:C18</xm:sqref>
+          <xm:sqref>C12:C30 C2:C11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$G$4:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F21:F39 E19 F2:F18</xm:sqref>
+          <xm:sqref>F12:F30 F2:F11</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Control_Inventario_Pole_Dance.xlsx
+++ b/Control_Inventario_Pole_Dance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cenicanaoff365-my.sharepoint.com/personal/iavar3_cenicanaoff365_onmicrosoft_com/Documents/Escritorio/Academia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF19AC0-A734-464B-A63B-8D632686E1F6}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{D8F039D2-5B30-42AD-85ED-01D7E78216B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4C6290E-3A34-4CED-9EC3-1E070C33FB80}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="183">
   <si>
     <t>PANEL DE CONTROL E INVENTARIOS - POLE DANCE ACADEMY</t>
   </si>
@@ -565,39 +565,6 @@
     <t>ACT-010</t>
   </si>
   <si>
-    <t>ACT-013</t>
-  </si>
-  <si>
-    <t>ACT-014</t>
-  </si>
-  <si>
-    <t>ACT-015</t>
-  </si>
-  <si>
-    <t>ACT-016</t>
-  </si>
-  <si>
-    <t>ACT-017</t>
-  </si>
-  <si>
-    <t>ACT-018</t>
-  </si>
-  <si>
-    <t>ACT-019</t>
-  </si>
-  <si>
-    <t>ACT-020</t>
-  </si>
-  <si>
-    <t>ACT-021</t>
-  </si>
-  <si>
-    <t>ACT-022</t>
-  </si>
-  <si>
-    <t>ACT-023</t>
-  </si>
-  <si>
     <t>Barra / Pole Profesional Dorado</t>
   </si>
   <si>
@@ -617,6 +584,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sistema de Sonido </t>
+  </si>
+  <si>
+    <t>ACT-011</t>
   </si>
 </sst>
 </file>
@@ -736,7 +706,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -770,11 +740,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9C5CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -828,30 +807,27 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -861,6 +837,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1594,20 +1588,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="23" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="24"/>
@@ -1615,76 +1609,76 @@
       <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="24"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="28" t="str">
+      <c r="C5" s="35" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:C, 3, FALSE), "⚠️ Código no encontrado")</f>
         <v>Top Velvet Negro</v>
       </c>
       <c r="D5" s="24"/>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="24"/>
-      <c r="C6" s="28" t="str">
+      <c r="C6" s="35" t="str">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:D, 4, FALSE), "-")</f>
         <v>M</v>
       </c>
       <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="24"/>
-      <c r="C7" s="33">
+      <c r="C7" s="32">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:F, 6, FALSE), 0)</f>
         <v>55000</v>
       </c>
       <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="24"/>
-      <c r="C8" s="26">
+      <c r="C8" s="31">
         <f>IFERROR(VLOOKUP(C4, '🏷️ Catálogo Productos'!A:J, 10, FALSE), 0)</f>
         <v>2</v>
       </c>
       <c r="D8" s="24"/>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="24"/>
-      <c r="C9" s="26">
+      <c r="C9" s="31">
         <f>SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F)</f>
         <v>0</v>
       </c>
       <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="24"/>
-      <c r="C10" s="35" t="str">
+      <c r="C10" s="34" t="str">
         <f>IF(C4="","", C4 &amp; (SUMIF('🛒 Ventas'!C:C, C4, '🛒 Ventas'!F:F) + 1))</f>
         <v>TM1</v>
       </c>
@@ -1696,40 +1690,40 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="30" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="24"/>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="30" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="24"/>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="24"/>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="30" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="32">
+      <c r="A15" s="28">
         <f>SUM('🏷️ Catálogo Productos'!J2:J12)</f>
         <v>14</v>
       </c>
       <c r="B15" s="24"/>
-      <c r="C15" s="23">
+      <c r="C15" s="29">
         <f>SUM('🏷️ Catálogo Productos'!K2:K12)</f>
         <v>405000</v>
       </c>
       <c r="D15" s="24"/>
-      <c r="E15" s="23">
+      <c r="E15" s="29">
         <f>SUM('🛒 Ventas'!H2:H58)</f>
         <v>0</v>
       </c>
       <c r="F15" s="24"/>
-      <c r="G15" s="23">
+      <c r="G15" s="29">
         <f>SUM('🏢 Activos Fijos'!H2:H11)</f>
         <v>5650000</v>
       </c>
@@ -1919,6 +1913,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
@@ -1935,14 +1937,6 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5008,7 +5002,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -5060,7 +5054,7 @@
         <v>141</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>42</v>
@@ -5093,7 +5087,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>42</v>
@@ -5126,7 +5120,7 @@
         <v>147</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>42</v>
@@ -5159,7 +5153,7 @@
         <v>152</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>42</v>
@@ -5184,7 +5178,7 @@
         <v>143</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -5321,7 +5315,7 @@
     </row>
     <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>166</v>
@@ -5357,7 +5351,7 @@
         <v>174</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>53</v>
@@ -5385,49 +5379,42 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="21" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="15"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E13" s="10">
         <f>SUM(E2:E11)</f>
         <v>13</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="11">
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="11">
         <f>SUM(H2:H11)</f>
         <v>5650000</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="22" t="str">
-        <f t="shared" ref="H13:H26" si="4">IF(E13="","",E13*G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="9"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
-        <v>184</v>
-      </c>
+    <row r="14" spans="1:10" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="15"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -5435,16 +5422,14 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H14:H27" si="4">IF(E14="","",E14*G14)</f>
         <v/>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="15" t="s">
-        <v>185</v>
-      </c>
+      <c r="A15" s="15"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -5459,9 +5444,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="15" t="s">
-        <v>175</v>
-      </c>
+      <c r="A16" s="15"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -5476,9 +5459,7 @@
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>176</v>
-      </c>
+      <c r="A17" s="15"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -5493,9 +5474,7 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="15" t="s">
-        <v>177</v>
-      </c>
+      <c r="A18" s="15"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -5510,9 +5489,7 @@
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
-        <v>178</v>
-      </c>
+      <c r="A19" s="15"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -5527,9 +5504,7 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="15" t="s">
-        <v>179</v>
-      </c>
+      <c r="A20" s="15"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -5544,9 +5519,7 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="A21" s="15"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -5561,9 +5534,7 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15" t="s">
-        <v>181</v>
-      </c>
+      <c r="A22" s="15"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -5578,9 +5549,7 @@
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
-        <v>182</v>
-      </c>
+      <c r="A23" s="15"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -5595,9 +5564,7 @@
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
-        <v>183</v>
-      </c>
+      <c r="A24" s="15"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -5612,9 +5579,7 @@
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>184</v>
-      </c>
+      <c r="A25" s="15"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -5628,10 +5593,8 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="15" t="s">
-        <v>185</v>
-      </c>
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="15"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -5643,6 +5606,21 @@
         <v/>
       </c>
       <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="15"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I27" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -5654,13 +5632,13 @@
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$I$4:$I$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C12:C30 C2:C11</xm:sqref>
+          <xm:sqref>C2:C31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
           <x14:formula1>
             <xm:f>'⚙️ Configuración'!$G$4:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F12:F30 F2:F11</xm:sqref>
+          <xm:sqref>F2:F31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
